--- a/output/pdf_financials_xlsx/BLST.xlsx
+++ b/output/pdf_financials_xlsx/BLST.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.150343</v>
+        <v>0.395543</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.068755</v>
+        <v>0.453355</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.239036</v>
+        <v>1.022251</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.150343</v>
+        <v>-0.395543</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.068755</v>
+        <v>-0.453355</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.239036</v>
+        <v>-1.022251</v>
       </c>
     </row>
     <row r="12">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.016719</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.304549</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.06945</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.016719</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.304549</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.06945</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.016719</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.324918</v>
+        <v>0.020369</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.09408900000000001</v>
+        <v>0.024639</v>
       </c>
     </row>
     <row r="49">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLST.xlsx
+++ b/output/pdf_financials_xlsx/BLST.xlsx
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.000396</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.016108</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008077000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.102032</v>
+        <v>0.102428</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.065495</v>
+        <v>0.049387</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.08492</v>
+        <v>-0.092997</v>
       </c>
     </row>
     <row r="107">
@@ -3410,7 +3410,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.000396</v>
       </c>
